--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92574428327</v>
+        <v>46157.93117736756</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93117736756</v>
+        <v>46157.93183551532</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93183551532</v>
+        <v>46157.93405715697</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93405715697</v>
+        <v>46157.93723808883</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93723808883</v>
+        <v>46158.28221580291</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28221580291</v>
+        <v>46158.29702137181</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29702137181</v>
+        <v>46158.29821329323</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29821329323</v>
+        <v>46158.33392612261</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33392612261</v>
+        <v>46158.36862400951</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/28. Сотрудники/2025 год/Богдановский- председатель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36862400951</v>
+        <v>46158.37293356292</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
